--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_21_9.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_21_9.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_3</t>
+          <t>model_21_9_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9893321817040207</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7056485813186906</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D2" t="n">
-        <v>0.987546987928158</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9888074000109335</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9959238213225162</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07133575006600029</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H2" t="n">
-        <v>1.968329292085573</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I2" t="n">
-        <v>0.009192551860112039</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01407250575020351</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01163252880515777</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4027593524470995</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2670875325918458</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N2" t="n">
-        <v>1.005954131141942</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2784580018016929</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P2" t="n">
-        <v>139.2807153475448</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q2" t="n">
-        <v>220.9453956137142</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_4</t>
+          <t>model_21_9_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9911406065556105</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7056316411904671</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9857935246523972</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9859770147095536</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9950735549566213</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05924280475638839</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H3" t="n">
-        <v>1.968442570801006</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01048692160810889</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01763116177899651</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01405900437845995</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4090891356747395</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2433984485496742</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N3" t="n">
-        <v>1.004944777736403</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2537604244086819</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P3" t="n">
-        <v>139.6522218901038</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q3" t="n">
-        <v>221.3169021562733</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_5</t>
+          <t>model_21_9_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9925765867312509</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7054481835091522</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9839433614097948</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9830246846027199</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9941839038682555</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04964039870980042</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H4" t="n">
-        <v>1.969669353160703</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01185267323985694</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0213431395540892</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01659787539731897</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L4" t="n">
-        <v>0.414721711814155</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2228012538335465</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N4" t="n">
-        <v>1.004143300429069</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2322863644714177</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P4" t="n">
-        <v>140.0059005733028</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q4" t="n">
-        <v>221.6705808394722</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_2</t>
+          <t>model_21_9_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9870602723475992</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7054378204621901</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9891599916735501</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9914114244201606</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9967060764113941</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08652801839357117</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H5" t="n">
-        <v>1.969738650903456</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008001866386225798</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01079845427795265</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009400142647843652</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3956174464056221</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2941564522385514</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N5" t="n">
-        <v>1.007222173573433</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3066793013981472</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P5" t="n">
-        <v>138.8945740108562</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q5" t="n">
-        <v>220.5592542770256</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_6</t>
+          <t>model_21_9_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9937135097312154</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7051457795315852</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9820350656576279</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9800304959182</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9932775123271276</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04203778937398833</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H6" t="n">
-        <v>1.971691529951136</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0132613370687382</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02510774630509066</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01918452003317923</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4197513889060086</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2050311912221854</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N6" t="n">
-        <v>1.00350873875467</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2137597935055901</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P6" t="n">
-        <v>140.3383726364575</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q6" t="n">
-        <v>222.0030529026269</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_1</t>
+          <t>model_21_9_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9842116066659692</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7049206601308192</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D7" t="n">
-        <v>0.990584105760028</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9936529808341262</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9973840391909357</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1055770589235304</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H7" t="n">
-        <v>1.973196904420638</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I7" t="n">
-        <v>0.006950615289773012</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007980135428377767</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007465384094347209</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3875188598781975</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3249262361268022</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N7" t="n">
-        <v>1.008812126512017</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3387590186887544</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P7" t="n">
-        <v>138.4966283527068</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q7" t="n">
-        <v>220.1613086188763</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_7</t>
+          <t>model_21_9_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9946104955497633</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7047613739382056</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9801021841691475</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9770540274555013</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9923718521452628</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03603964107511845</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H8" t="n">
-        <v>1.974262051924091</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I8" t="n">
-        <v>0.014688149571593</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02885007334237819</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02176907752851697</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4242513884295047</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1898410942739175</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N8" t="n">
-        <v>1.003008095507109</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O8" t="n">
-        <v>0.197923022682399</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P8" t="n">
-        <v>140.6462716107231</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q8" t="n">
-        <v>222.3109518768925</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_8</t>
+          <t>model_21_9_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9953151802847774</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7043236074188578</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D9" t="n">
-        <v>0.97817353711025</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9741397396810707</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9914804127912243</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03132741100730504</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H9" t="n">
-        <v>1.977189398654699</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01611183630749971</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03251422032373059</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02431305186928479</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4282846610057303</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1769955112631534</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N9" t="n">
-        <v>1.002614783096868</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O9" t="n">
-        <v>0.184530576608844</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P9" t="n">
-        <v>140.9265236273002</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q9" t="n">
-        <v>222.5912038934697</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_0</t>
+          <t>model_21_9_15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9806451004166798</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7039958220207637</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9917657358900239</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E10" t="n">
-        <v>0.995352848939178</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9979113284024369</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1294263026347798</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H10" t="n">
-        <v>1.979381301121067</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I10" t="n">
-        <v>0.006078360755143584</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0058428836989945</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K10" t="n">
-        <v>0.005960615185339538</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3782742469727862</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3597586727721513</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N10" t="n">
-        <v>1.010802734651155</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3750743442751801</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P10" t="n">
-        <v>138.0892873029199</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q10" t="n">
-        <v>219.7539675690894</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_9</t>
+          <t>model_21_9_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9958660252349264</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7038544430082926</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9762731842109615</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9713208509599394</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9906136749128928</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02764390828925056</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H11" t="n">
-        <v>1.980326703228452</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01751463688927413</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J11" t="n">
-        <v>0.03605842165104093</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02678653356229954</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4319013242628158</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1662645731635292</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N11" t="n">
-        <v>1.002307334752599</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1733428002582147</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P11" t="n">
-        <v>141.1766997806457</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q11" t="n">
-        <v>222.8413800468151</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_10</t>
+          <t>model_21_9_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.996294012637619</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7033706390929952</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9744191966582164</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9686198975914869</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9897789080426784</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02478195455674508</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H12" t="n">
-        <v>1.983561902237757</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01888321154641655</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J12" t="n">
-        <v>0.03945434233485959</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K12" t="n">
-        <v>0.02916877694063807</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4351577597780639</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1574228527144172</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N12" t="n">
-        <v>1.002068458062724</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1641246694646994</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P12" t="n">
-        <v>141.3952790590195</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q12" t="n">
-        <v>223.0599593251889</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_11</t>
+          <t>model_21_9_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9966240778569464</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7028847204383661</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9726282119018897</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9660524332990182</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9889816939885843</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G13" t="n">
-        <v>0.02257480691529119</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H13" t="n">
-        <v>1.986811242518712</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02020527886300011</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J13" t="n">
-        <v>0.04268242660969313</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K13" t="n">
-        <v>0.03144385273634662</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4380849748635487</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1502491494661158</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N13" t="n">
-        <v>1.001884235614728</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1566455668175049</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P13" t="n">
-        <v>141.5818414654964</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q13" t="n">
-        <v>223.2465217316658</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="14">
@@ -1177,657 +1177,657 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9968763310076092</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7024060683791498</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9709112637823618</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E14" t="n">
-        <v>0.963628306651434</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9882256166834421</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0208879889352907</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H14" t="n">
-        <v>1.990011991042682</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I14" t="n">
-        <v>0.02147269388988913</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J14" t="n">
-        <v>0.04573029182605713</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K14" t="n">
-        <v>0.03360153318337274</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4407168350004446</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1445267758420241</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N14" t="n">
-        <v>1.001743443158544</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1506795799012893</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P14" t="n">
-        <v>141.737161954603</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q14" t="n">
-        <v>223.4018422207725</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_13</t>
+          <t>model_21_9_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9970669128839611</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7019414283497318</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9692761575270085</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9613515383421271</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9875126446294231</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01961356705057636</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H15" t="n">
-        <v>1.99311904105887</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02267969497223097</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J15" t="n">
-        <v>0.04859288274826461</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K15" t="n">
-        <v>0.03563620060397944</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4430884422247688</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1400484453700803</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N15" t="n">
-        <v>1.001637071878719</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1460105976297327</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P15" t="n">
-        <v>141.8630675114903</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q15" t="n">
-        <v>223.5277477776598</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_14</t>
+          <t>model_21_9_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9972088406079255</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7014955691913987</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9677291260985685</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9592245486710392</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9868439918548371</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01866449570690925</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H16" t="n">
-        <v>1.996100503303636</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I16" t="n">
-        <v>0.02382168106789318</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J16" t="n">
-        <v>0.05126715632243386</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K16" t="n">
-        <v>0.03754439042499647</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4452264392376714</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1366180650825843</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N16" t="n">
-        <v>1.001557856404879</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1424341789515319</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P16" t="n">
-        <v>141.9622643701884</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q16" t="n">
-        <v>223.6269446363578</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_15</t>
+          <t>model_21_9_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9973124962982837</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C17" t="n">
-        <v>0.701071602948888</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D17" t="n">
-        <v>0.966272693322193</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9572451835824389</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F17" t="n">
-        <v>0.986219554752979</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01797134962819347</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H17" t="n">
-        <v>1.99893556751949</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I17" t="n">
-        <v>0.02489678914217758</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J17" t="n">
-        <v>0.05375582085241705</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K17" t="n">
-        <v>0.03932639831746164</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L17" t="n">
-        <v>0.447150454927169</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1340572624970146</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N17" t="n">
-        <v>1.001500002066074</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1397643576983023</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P17" t="n">
-        <v>142.0379529529772</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q17" t="n">
-        <v>223.7026332191466</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_16</t>
+          <t>model_21_9_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9973862129017127</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7006715384734349</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9649084464153952</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9554096821103697</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9856387936217325</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01747840636162997</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H18" t="n">
-        <v>2.001610800508973</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I18" t="n">
-        <v>0.02590384754446512</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J18" t="n">
-        <v>0.05606360501743978</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0409837644740187</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4488838041725353</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1322059240791802</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N18" t="n">
-        <v>1.001458857915323</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1378342039712219</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P18" t="n">
-        <v>142.0935781643081</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q18" t="n">
-        <v>223.7582584304775</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_17</t>
+          <t>model_21_9_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9974366790863788</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7002963114017851</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9636357185808202</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9537139071482724</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9851006514113583</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01714093875239223</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H19" t="n">
-        <v>2.004119945664857</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I19" t="n">
-        <v>0.02684334849055293</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J19" t="n">
-        <v>0.05819571041998038</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0425195054850857</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4504475083672526</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1309234079620304</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N19" t="n">
-        <v>1.001430690742486</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1364970884877906</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P19" t="n">
-        <v>142.1325711952556</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q19" t="n">
-        <v>223.797251461425</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_18</t>
+          <t>model_21_9_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9974691617614014</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6999462345228937</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9624524831808557</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9521504734111551</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9846032064773756</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G20" t="n">
-        <v>0.01692372695494697</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H20" t="n">
-        <v>2.006460911365959</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0277167880017446</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J20" t="n">
-        <v>0.06016142261170863</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K20" t="n">
-        <v>0.04393910530672662</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4518545195567299</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1300912255109735</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N20" t="n">
-        <v>1.001412560877357</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1356294783069371</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P20" t="n">
-        <v>142.1580773597097</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q20" t="n">
-        <v>223.8227576258791</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_19</t>
+          <t>model_21_9_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9974879355391396</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6996210710666175</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D21" t="n">
-        <v>0.961356904930854</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9507139450031349</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9841450305495322</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01679818661676662</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H21" t="n">
-        <v>2.008635280895319</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I21" t="n">
-        <v>0.02852552084660582</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J21" t="n">
-        <v>0.06196757616869654</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K21" t="n">
-        <v>0.04524663991209345</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L21" t="n">
-        <v>0.453122697010776</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1296078185016885</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N21" t="n">
-        <v>1.001402082489782</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1351254916604763</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P21" t="n">
-        <v>142.172968675754</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q21" t="n">
-        <v>223.8376489419234</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_20</t>
+          <t>model_21_9_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9974962936243479</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6993201590879254</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9603449592729693</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9493959210797618</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9837238127331023</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G22" t="n">
-        <v>0.01674229606249368</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H22" t="n">
-        <v>2.010647480682405</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0292725178691779</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J22" t="n">
-        <v>0.06362473351003745</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K22" t="n">
-        <v>0.04644870409292361</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4542668567692637</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1293920247252267</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N22" t="n">
-        <v>1.001397417511992</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1349005110961959</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P22" t="n">
-        <v>142.1796341261637</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q22" t="n">
-        <v>223.8443143923332</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_21</t>
+          <t>model_21_9_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9974968843176644</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C23" t="n">
-        <v>0.699042605035478</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9594126932837865</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9481888116984085</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9833373706496412</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0167383460935666</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H23" t="n">
-        <v>2.01250348590914</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I23" t="n">
-        <v>0.02996069703447068</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J23" t="n">
-        <v>0.06514243750435628</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K23" t="n">
-        <v>0.04755152588339556</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4552974786800176</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1293767602530169</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N23" t="n">
-        <v>1.001397087822699</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1348845967838022</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P23" t="n">
-        <v>142.1801060369386</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q23" t="n">
-        <v>223.844786303108</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_22</t>
+          <t>model_21_9_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9974918133582475</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C24" t="n">
-        <v>0.698787325779856</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D24" t="n">
-        <v>0.958555848293443</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9470862939449551</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9829836486717822</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G24" t="n">
-        <v>0.01677225562253586</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H24" t="n">
-        <v>2.014210539466936</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I24" t="n">
-        <v>0.03059320200309754</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J24" t="n">
-        <v>0.06652863797969982</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K24" t="n">
-        <v>0.04856097159763532</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4562266204834514</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1295077434848429</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N24" t="n">
-        <v>1.001399918125629</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1350211562429798</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P24" t="n">
-        <v>142.1760584175218</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q24" t="n">
-        <v>223.8407386836913</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_21_9_23</t>
+          <t>model_21_9_11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9974826968554027</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C25" t="n">
-        <v>0.698553088396525</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D25" t="n">
-        <v>0.957770458236806</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9460801603038704</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9826604510733208</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G25" t="n">
-        <v>0.01683321771903743</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H25" t="n">
-        <v>2.015776885927836</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I25" t="n">
-        <v>0.03117296044100805</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J25" t="n">
-        <v>0.06779365428185197</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K25" t="n">
-        <v>0.04948330736143002</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4570626454847178</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1297428908227246</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N25" t="n">
-        <v>1.001405006406287</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1352663142898572</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P25" t="n">
-        <v>142.168802199137</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q25" t="n">
-        <v>223.8334824653064</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9974707915621451</v>
+        <v>0.9989032789407235</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6983386778597076</v>
+        <v>0.6851986482775998</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9570513892517792</v>
+        <v>0.9894862304463019</v>
       </c>
       <c r="E26" t="n">
-        <v>0.945163580812668</v>
+        <v>0.9959103592484642</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9823655629774533</v>
+        <v>0.9926893261778705</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01691282846986916</v>
+        <v>0.0006510609966694511</v>
       </c>
       <c r="H26" t="n">
-        <v>2.017210650174803</v>
+        <v>0.1868796810927376</v>
       </c>
       <c r="I26" t="n">
-        <v>0.03170376205733368</v>
+        <v>0.001844603991348169</v>
       </c>
       <c r="J26" t="n">
-        <v>0.06894607375302619</v>
+        <v>0.0005872249032164898</v>
       </c>
       <c r="K26" t="n">
-        <v>0.05032485395221738</v>
+        <v>0.001215914447267572</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4578169738132941</v>
+        <v>0.01016841032169391</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1300493309089638</v>
+        <v>0.02551589694032822</v>
       </c>
       <c r="N26" t="n">
-        <v>1.001411651221128</v>
+        <v>1.000506178950435</v>
       </c>
       <c r="O26" t="n">
-        <v>0.135585800164986</v>
+        <v>0.02660216149826623</v>
       </c>
       <c r="P26" t="n">
-        <v>142.1593657279041</v>
+        <v>166.6738144465282</v>
       </c>
       <c r="Q26" t="n">
-        <v>223.8240459940736</v>
+        <v>259.3083771365115</v>
       </c>
     </row>
   </sheetData>
